--- a/app/src/main/res/raw/pregnancy_outcome_form.xlsx
+++ b/app/src/main/res/raw/pregnancy_outcome_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27795" windowHeight="12195" tabRatio="500"/>
+    <workbookView windowWidth="22620" windowHeight="12090" tabRatio="500" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -901,7 +901,7 @@
     <t>repeat_name</t>
   </si>
   <si>
-    <t>xml_node_name</t>
+    <t>repeat_xml_node</t>
   </si>
   <si>
     <t>rawPregnancyOutcome</t>
@@ -927,10 +927,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -970,9 +970,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -985,6 +991,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="Arial"/>
@@ -992,24 +1021,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1031,43 +1045,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -1084,8 +1061,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1093,14 +1071,21 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1115,7 +1100,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1165,7 +1165,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1177,37 +1255,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1219,85 +1315,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1309,43 +1339,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1454,15 +1454,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1474,6 +1465,39 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1493,17 +1517,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1511,8 +1531,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1531,171 +1551,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3823,8 +3823,9 @@
     <col min="1" max="1" width="21.7238095238095" customWidth="1"/>
     <col min="2" max="2" width="28.2666666666667" customWidth="1"/>
     <col min="3" max="4" width="29.7238095238095" customWidth="1"/>
-    <col min="5" max="5" width="34.7428571428571" customWidth="1"/>
-    <col min="6" max="7" width="12.5428571428571" customWidth="1"/>
+    <col min="5" max="5" width="19.9142857142857" customWidth="1"/>
+    <col min="6" max="6" width="16.7428571428571" customWidth="1"/>
+    <col min="7" max="7" width="17.0190476190476" customWidth="1"/>
     <col min="8" max="8" width="27" customWidth="1"/>
   </cols>
   <sheetData>

--- a/app/src/main/res/raw/pregnancy_outcome_form.xlsx
+++ b/app/src/main/res/raw/pregnancy_outcome_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22620" windowHeight="12090" tabRatio="500" activeTab="2"/>
+    <workbookView windowWidth="22770" windowHeight="12315" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="289">
   <si>
     <t>group</t>
   </si>
@@ -284,9 +284,6 @@
   </si>
   <si>
     <t>start repeat</t>
-  </si>
-  <si>
-    <t>$child_outcomes</t>
   </si>
   <si>
     <t>4. Child's Outcomes</t>
@@ -928,9 +925,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -973,29 +970,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1015,31 +990,44 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1053,6 +1041,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
@@ -1061,24 +1072,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1100,9 +1096,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1111,13 +1115,6 @@
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1165,19 +1162,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1189,13 +1192,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1213,7 +1210,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1225,19 +1306,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1249,103 +1342,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1454,6 +1451,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1469,11 +1477,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1487,17 +1516,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1519,183 +1542,157 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="13" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2543,20 +2540,18 @@
         <v>77</v>
       </c>
       <c r="F12" s="37"/>
-      <c r="G12" s="37" t="s">
+      <c r="G12" s="37"/>
+      <c r="H12" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="H12" s="29" t="s">
+      <c r="I12" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="I12" s="29" t="s">
+      <c r="J12" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="J12" s="44" t="s">
+      <c r="K12" s="45" t="s">
         <v>81</v>
-      </c>
-      <c r="K12" s="45" t="s">
-        <v>82</v>
       </c>
       <c r="L12" s="46"/>
       <c r="M12" s="46"/>
@@ -2570,25 +2565,25 @@
     <row r="13" spans="1:14">
       <c r="A13" s="1"/>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="27" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
         <v>84</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>85</v>
       </c>
-      <c r="I13" t="s">
+      <c r="J13" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="42" t="s">
         <v>87</v>
-      </c>
-      <c r="K13" s="42" t="s">
-        <v>88</v>
       </c>
       <c r="L13" s="43"/>
       <c r="M13" s="43"/>
@@ -2601,7 +2596,7 @@
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
       <c r="D14" s="31" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>20</v>
@@ -2609,16 +2604,16 @@
       <c r="F14" s="31"/>
       <c r="G14" s="31"/>
       <c r="H14" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>89</v>
+      </c>
+      <c r="K14" s="47" t="s">
         <v>90</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="K14" s="47" t="s">
-        <v>91</v>
       </c>
       <c r="L14" s="48"/>
       <c r="M14" s="48"/>
@@ -2637,22 +2632,22 @@
     <row r="15" spans="1:15">
       <c r="A15" s="1"/>
       <c r="D15" s="31" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
+        <v>92</v>
+      </c>
+      <c r="I15" t="s">
         <v>93</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="42" t="s">
         <v>95</v>
-      </c>
-      <c r="K15" s="42" t="s">
-        <v>96</v>
       </c>
       <c r="L15" s="43"/>
       <c r="M15" s="43"/>
@@ -2666,51 +2661,51 @@
     <row r="16" spans="1:14">
       <c r="A16" s="1"/>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" t="s">
         <v>98</v>
       </c>
-      <c r="I16" t="s">
+      <c r="J16" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="42" t="s">
         <v>100</v>
-      </c>
-      <c r="K16" s="42" t="s">
-        <v>101</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="43"/>
       <c r="N16" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1"/>
       <c r="D17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
       </c>
       <c r="F17" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" t="s">
         <v>104</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>105</v>
       </c>
-      <c r="I17" t="s">
+      <c r="J17" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="42" t="s">
         <v>107</v>
-      </c>
-      <c r="K17" s="42" t="s">
-        <v>108</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="43"/>
@@ -2721,22 +2716,22 @@
     <row r="18" spans="1:14">
       <c r="A18" s="1"/>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E18" t="s">
         <v>52</v>
       </c>
       <c r="H18" t="s">
+        <v>109</v>
+      </c>
+      <c r="I18" t="s">
         <v>110</v>
       </c>
-      <c r="I18" t="s">
+      <c r="J18" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="J18" s="2" t="s">
+      <c r="K18" s="42" t="s">
         <v>112</v>
-      </c>
-      <c r="K18" s="42" t="s">
-        <v>113</v>
       </c>
       <c r="L18" s="43"/>
       <c r="M18" s="43"/>
@@ -2747,25 +2742,25 @@
     <row r="19" spans="1:16">
       <c r="A19" s="1"/>
       <c r="D19" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" t="s">
         <v>114</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" s="27" t="s">
         <v>115</v>
       </c>
-      <c r="F19" s="27" t="s">
+      <c r="H19" t="s">
         <v>116</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>117</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="J19" s="49" t="s">
+      <c r="K19" s="42" t="s">
         <v>119</v>
-      </c>
-      <c r="K19" s="42" t="s">
-        <v>120</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="43"/>
@@ -2773,7 +2768,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="55" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" s="26" customFormat="1" spans="1:17">
@@ -2784,7 +2779,7 @@
         <v>76</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
@@ -2801,29 +2796,29 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B21" s="33"/>
       <c r="C21" s="33"/>
       <c r="D21" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="E21" s="33" t="s">
         <v>124</v>
-      </c>
-      <c r="E21" s="33" t="s">
-        <v>125</v>
       </c>
       <c r="F21" s="38"/>
       <c r="G21" s="38"/>
       <c r="H21" s="33" t="s">
+        <v>125</v>
+      </c>
+      <c r="I21" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="I21" s="33" t="s">
+      <c r="J21" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="J21" s="50" t="s">
+      <c r="K21" s="51" t="s">
         <v>128</v>
-      </c>
-      <c r="K21" s="51" t="s">
-        <v>129</v>
       </c>
       <c r="L21" s="52"/>
       <c r="M21" s="52"/>
@@ -2839,29 +2834,29 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
       <c r="D22" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E22" s="31" t="s">
         <v>130</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>131</v>
       </c>
       <c r="F22" s="39"/>
       <c r="G22" s="39"/>
       <c r="H22" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="I22" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="I22" s="31" t="s">
+      <c r="J22" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="J22" s="50" t="s">
+      <c r="K22" s="47" t="s">
         <v>134</v>
-      </c>
-      <c r="K22" s="47" t="s">
-        <v>135</v>
       </c>
       <c r="L22" s="48"/>
       <c r="M22" s="48"/>
@@ -2877,29 +2872,29 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
       <c r="D23" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" s="31" t="s">
         <v>136</v>
-      </c>
-      <c r="E23" s="31" t="s">
-        <v>137</v>
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="31"/>
       <c r="H23" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="I23" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="J23" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="K23" s="47" t="s">
         <v>138</v>
-      </c>
-      <c r="I23" s="31" t="s">
-        <v>138</v>
-      </c>
-      <c r="J23" s="50" t="s">
-        <v>138</v>
-      </c>
-      <c r="K23" s="47" t="s">
-        <v>139</v>
       </c>
       <c r="L23" s="48"/>
       <c r="M23" s="48"/>
@@ -2915,12 +2910,12 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E24" s="31" t="s">
         <v>20</v>
@@ -2928,16 +2923,16 @@
       <c r="F24" s="31"/>
       <c r="G24" s="31"/>
       <c r="H24" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="J24" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="K24" s="47" t="s">
         <v>141</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="J24" s="50" t="s">
-        <v>141</v>
-      </c>
-      <c r="K24" s="47" t="s">
-        <v>142</v>
       </c>
       <c r="L24" s="48"/>
       <c r="M24" s="48"/>
@@ -2953,12 +2948,12 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="34" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>20</v>
@@ -2966,16 +2961,16 @@
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
       <c r="H25" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="J25" s="50" t="s">
+        <v>143</v>
+      </c>
+      <c r="K25" s="47" t="s">
         <v>144</v>
-      </c>
-      <c r="I25" s="31" t="s">
-        <v>144</v>
-      </c>
-      <c r="J25" s="50" t="s">
-        <v>144</v>
-      </c>
-      <c r="K25" s="47" t="s">
-        <v>145</v>
       </c>
       <c r="L25" s="48"/>
       <c r="M25" s="48"/>
@@ -2991,12 +2986,12 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B26" s="36"/>
       <c r="C26" s="36"/>
       <c r="D26" s="36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E26" s="36" t="s">
         <v>20</v>
@@ -3004,16 +2999,16 @@
       <c r="F26" s="40"/>
       <c r="G26" s="40"/>
       <c r="H26" s="36" t="s">
+        <v>146</v>
+      </c>
+      <c r="I26" s="36" t="s">
         <v>147</v>
       </c>
-      <c r="I26" s="36" t="s">
+      <c r="J26" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="J26" s="50" t="s">
+      <c r="K26" s="53" t="s">
         <v>149</v>
-      </c>
-      <c r="K26" s="53" t="s">
-        <v>150</v>
       </c>
       <c r="L26" s="54"/>
       <c r="M26" s="54"/>
@@ -3111,7 +3106,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
@@ -3140,373 +3135,373 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B2" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>152</v>
       </c>
-      <c r="B2" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>153</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D3" t="s">
         <v>157</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="F4" s="19" t="s">
         <v>164</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>165</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="F5" s="19" t="s">
         <v>169</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>170</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="F6" s="20" t="s">
         <v>174</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>175</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="21" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="22" t="s">
         <v>180</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="G7" s="23" t="s">
         <v>181</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B8" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="D8" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="E8" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="F8" s="3" t="s">
         <v>186</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B9" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="C9" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="D9" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="24" t="s">
         <v>190</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="F9" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="D10" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="E10" s="24" t="s">
+      <c r="F10" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="D11" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="E11" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="F11" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="E12" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="F12" s="3" t="s">
         <v>206</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C13" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="D13" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="E13" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="F13" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B14" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="C14" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="D14" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="F14" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="8" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="D15" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="F15" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" s="11" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>223</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="D16" t="s">
         <v>224</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B17" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="D17" t="s">
         <v>229</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B18" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C18" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="D18" t="s">
         <v>234</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B19" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="D19" t="s">
         <v>239</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3514,19 +3509,19 @@
         <v>65</v>
       </c>
       <c r="B20" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" t="s">
         <v>244</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3534,19 +3529,19 @@
         <v>65</v>
       </c>
       <c r="B21" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="D21" t="s">
         <v>249</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3554,19 +3549,19 @@
         <v>65</v>
       </c>
       <c r="B22" s="16" t="s">
+        <v>252</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="D22" t="s">
         <v>254</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3574,19 +3569,19 @@
         <v>65</v>
       </c>
       <c r="B23" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>258</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="D23" t="s">
         <v>259</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3594,19 +3589,19 @@
         <v>65</v>
       </c>
       <c r="B24" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="D24" t="s">
         <v>264</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="3" t="s">
         <v>266</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3614,19 +3609,19 @@
         <v>65</v>
       </c>
       <c r="B25" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>268</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" t="s">
         <v>269</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>271</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3634,19 +3629,19 @@
         <v>65</v>
       </c>
       <c r="B26" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="C26" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="D26" t="s">
+        <v>214</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="D26" t="s">
-        <v>215</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3831,45 +3826,45 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>277</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" t="s">
         <v>279</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>280</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B2" t="s">
         <v>284</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>285</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>288</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -3878,7 +3873,7 @@
         <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>

--- a/app/src/main/res/raw/pregnancy_outcome_form.xlsx
+++ b/app/src/main/res/raw/pregnancy_outcome_form.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22770" windowHeight="12315" tabRatio="500"/>
+    <workbookView windowWidth="27795" windowHeight="12315" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="columns" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="290">
   <si>
     <t>group</t>
   </si>
@@ -284,6 +284,9 @@
   </si>
   <si>
     <t>start repeat</t>
+  </si>
+  <si>
+    <t>$external</t>
   </si>
   <si>
     <t>4. Child's Outcomes</t>
@@ -925,9 +928,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -967,8 +970,31 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -981,8 +1007,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -990,7 +1047,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1004,84 +1076,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="Arial"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1103,18 +1107,17 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1162,7 +1165,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1174,13 +1183,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1198,79 +1213,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1288,7 +1243,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1300,19 +1297,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1324,25 +1333,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1453,41 +1456,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1516,6 +1487,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -1540,159 +1537,165 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="12" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2540,18 +2543,20 @@
         <v>77</v>
       </c>
       <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
+      <c r="G12" s="37" t="s">
+        <v>78</v>
+      </c>
       <c r="H12" s="29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I12" s="29" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J12" s="44" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K12" s="45" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L12" s="46"/>
       <c r="M12" s="46"/>
@@ -2565,25 +2570,25 @@
     <row r="13" spans="1:14">
       <c r="A13" s="1"/>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E13" t="s">
         <v>64</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" s="42" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L13" s="43"/>
       <c r="M13" s="43"/>
@@ -2596,7 +2601,7 @@
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
       <c r="D14" s="31" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>20</v>
@@ -2604,16 +2609,16 @@
       <c r="F14" s="31"/>
       <c r="G14" s="31"/>
       <c r="H14" s="31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I14" s="31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J14" s="31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K14" s="47" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L14" s="48"/>
       <c r="M14" s="48"/>
@@ -2632,22 +2637,22 @@
     <row r="15" spans="1:15">
       <c r="A15" s="1"/>
       <c r="D15" s="31" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E15" t="s">
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K15" s="42" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L15" s="43"/>
       <c r="M15" s="43"/>
@@ -2661,51 +2666,51 @@
     <row r="16" spans="1:14">
       <c r="A16" s="1"/>
       <c r="D16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E16" t="s">
         <v>20</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="K16" s="42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L16" s="43"/>
       <c r="M16" s="43"/>
       <c r="N16" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="1"/>
       <c r="D17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
         <v>64</v>
       </c>
       <c r="F17" s="27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I17" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K17" s="42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L17" s="43"/>
       <c r="M17" s="43"/>
@@ -2716,22 +2721,22 @@
     <row r="18" spans="1:14">
       <c r="A18" s="1"/>
       <c r="D18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" t="s">
         <v>52</v>
       </c>
       <c r="H18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K18" s="42" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L18" s="43"/>
       <c r="M18" s="43"/>
@@ -2742,25 +2747,25 @@
     <row r="19" spans="1:16">
       <c r="A19" s="1"/>
       <c r="D19" s="31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J19" s="49" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K19" s="42" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L19" s="43"/>
       <c r="M19" s="43"/>
@@ -2768,7 +2773,7 @@
         <v>1</v>
       </c>
       <c r="P19" s="55" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" s="26" customFormat="1" spans="1:17">
@@ -2779,7 +2784,7 @@
         <v>76</v>
       </c>
       <c r="E20" s="29" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F20" s="37"/>
       <c r="G20" s="37"/>
@@ -2796,29 +2801,29 @@
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B21" s="33"/>
       <c r="C21" s="33"/>
       <c r="D21" s="33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F21" s="38"/>
       <c r="G21" s="38"/>
       <c r="H21" s="33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J21" s="50" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L21" s="52"/>
       <c r="M21" s="52"/>
@@ -2834,29 +2839,29 @@
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
       <c r="D22" s="31" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F22" s="39"/>
       <c r="G22" s="39"/>
       <c r="H22" s="31" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I22" s="31" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J22" s="50" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K22" s="47" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L22" s="48"/>
       <c r="M22" s="48"/>
@@ -2872,29 +2877,29 @@
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
       <c r="D23" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="31"/>
       <c r="H23" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I23" s="31" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J23" s="50" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K23" s="47" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L23" s="48"/>
       <c r="M23" s="48"/>
@@ -2910,12 +2915,12 @@
     </row>
     <row r="24" spans="1:18">
       <c r="A24" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E24" s="31" t="s">
         <v>20</v>
@@ -2923,16 +2928,16 @@
       <c r="F24" s="31"/>
       <c r="G24" s="31"/>
       <c r="H24" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J24" s="50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K24" s="47" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L24" s="48"/>
       <c r="M24" s="48"/>
@@ -2948,12 +2953,12 @@
     </row>
     <row r="25" spans="1:18">
       <c r="A25" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E25" s="31" t="s">
         <v>20</v>
@@ -2961,16 +2966,16 @@
       <c r="F25" s="31"/>
       <c r="G25" s="31"/>
       <c r="H25" s="31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I25" s="31" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J25" s="50" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K25" s="47" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L25" s="48"/>
       <c r="M25" s="48"/>
@@ -2986,12 +2991,12 @@
     </row>
     <row r="26" spans="1:18">
       <c r="A26" s="35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B26" s="36"/>
       <c r="C26" s="36"/>
       <c r="D26" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E26" s="36" t="s">
         <v>20</v>
@@ -2999,16 +3004,16 @@
       <c r="F26" s="40"/>
       <c r="G26" s="40"/>
       <c r="H26" s="36" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J26" s="50" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K26" s="53" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L26" s="54"/>
       <c r="M26" s="54"/>
@@ -3106,7 +3111,7 @@
         <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C1" t="s">
         <v>7</v>
@@ -3135,373 +3140,373 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B3" s="1" t="b">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G3" s="1"/>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G4" s="4"/>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G5" s="4"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="21" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D17" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D19" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -3509,19 +3514,19 @@
         <v>65</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3529,19 +3534,19 @@
         <v>65</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D21" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3549,19 +3554,19 @@
         <v>65</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D22" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3569,19 +3574,19 @@
         <v>65</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3589,19 +3594,19 @@
         <v>65</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D24" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3609,19 +3614,19 @@
         <v>65</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D25" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -3629,19 +3634,19 @@
         <v>65</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C26" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D26" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -3826,45 +3831,45 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F2" s="1">
         <v>1</v>
@@ -3873,7 +3878,7 @@
         <v>76</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
